--- a/datos/motores.xlsx
+++ b/datos/motores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Electrical_Engineering\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2C4CE6-9B19-4BEA-81B8-C0B872F6BB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4BE601-45EC-44E9-B4C3-017CC4DDDD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CF66B361-FEBB-41C8-94E9-5375418F99E3}"/>
   </bookViews>
@@ -34,54 +34,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>TAG</t>
   </si>
   <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>VOLTAJE</t>
+  </si>
+  <si>
+    <t>FP</t>
+  </si>
+  <si>
+    <t>EFICIENCIA</t>
+  </si>
+  <si>
+    <t>M-001</t>
+  </si>
+  <si>
+    <t>M-002</t>
+  </si>
+  <si>
+    <t>M-003</t>
+  </si>
+  <si>
+    <t>CORRIENTE_PLACA_A</t>
+  </si>
+  <si>
     <t>DESCRIPCION</t>
   </si>
   <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>VOLTAJE</t>
-  </si>
-  <si>
-    <t>FP</t>
-  </si>
-  <si>
-    <t>EFICIENCIA</t>
-  </si>
-  <si>
-    <t>M-001</t>
+    <t>CORRIENTE_L1_A</t>
+  </si>
+  <si>
+    <t>CORRIENTE_L2_A</t>
+  </si>
+  <si>
+    <t>CORRIENTE_L3_A</t>
+  </si>
+  <si>
+    <t>VOLTAJE_L1_L2_V</t>
+  </si>
+  <si>
+    <t>VOLTAJE_L2_L3_V</t>
+  </si>
+  <si>
+    <t>VOLTAJE_L3_L1_V</t>
+  </si>
+  <si>
+    <t>ESTADO</t>
   </si>
   <si>
     <t>Bomba de agua</t>
   </si>
   <si>
-    <t>M-002</t>
+    <t>Operando</t>
   </si>
   <si>
     <t>Ventilador</t>
   </si>
   <si>
-    <t>M-003</t>
-  </si>
-  <si>
     <t>Bomba condensado</t>
-  </si>
-  <si>
-    <t>CORRIENTE_PLACA_A</t>
-  </si>
-  <si>
-    <t>CORRIENTE_MEDIDA_A</t>
-  </si>
-  <si>
-    <t>ESTADO</t>
-  </si>
-  <si>
-    <t>Operando</t>
   </si>
 </sst>
 </file>
@@ -130,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -138,15 +153,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -465,135 +471,197 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9F3007C-4CCE-4FA5-A545-AD73C08BCFA6}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" style="7" customWidth="1"/>
-    <col min="9" max="9" width="9.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.7265625" style="2"/>
+    <col min="3" max="3" width="4.08984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.26953125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="18.7265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="19.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>14</v>
+      <c r="B2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="3">
+        <v>125</v>
+      </c>
+      <c r="D2" s="3">
+        <v>480</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.94</v>
+      </c>
+      <c r="G2" s="3">
+        <v>140</v>
+      </c>
+      <c r="H2" s="3">
+        <v>118</v>
+      </c>
+      <c r="I2" s="3">
+        <v>120</v>
+      </c>
+      <c r="J2" s="3">
+        <v>123</v>
+      </c>
+      <c r="K2" s="3">
+        <v>478</v>
+      </c>
+      <c r="L2" s="3">
+        <v>481</v>
+      </c>
+      <c r="M2" s="3">
+        <v>479</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3">
+        <v>75</v>
+      </c>
+      <c r="D3" s="3">
+        <v>480</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.93</v>
+      </c>
+      <c r="G3" s="3">
+        <v>82</v>
+      </c>
+      <c r="H3" s="3">
+        <v>74</v>
+      </c>
+      <c r="I3" s="3">
+        <v>76</v>
+      </c>
+      <c r="J3" s="3">
+        <v>79</v>
+      </c>
+      <c r="K3" s="3">
+        <v>477</v>
+      </c>
+      <c r="L3" s="3">
+        <v>480</v>
+      </c>
+      <c r="M3" s="3">
+        <v>482</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5">
-        <v>125</v>
-      </c>
-      <c r="D2" s="5">
+      <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3">
+        <v>30</v>
+      </c>
+      <c r="D4" s="3">
         <v>480</v>
       </c>
-      <c r="E2" s="6">
-        <v>0.88</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0.94</v>
-      </c>
-      <c r="G2" s="5">
-        <v>140</v>
-      </c>
-      <c r="H2" s="5">
-        <v>120</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5">
-        <v>75</v>
-      </c>
-      <c r="D3" s="5">
-        <v>480</v>
-      </c>
-      <c r="E3" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0.93</v>
-      </c>
-      <c r="G3" s="5">
-        <v>82</v>
-      </c>
-      <c r="H3" s="5">
-        <v>76</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="5">
-        <v>30</v>
-      </c>
-      <c r="D4" s="5">
-        <v>480</v>
-      </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>0.87</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>0.91</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="3">
         <v>35</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="3">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3">
         <v>32</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>15</v>
+      <c r="J4" s="3">
+        <v>33</v>
+      </c>
+      <c r="K4" s="3">
+        <v>479</v>
+      </c>
+      <c r="L4" s="3">
+        <v>478</v>
+      </c>
+      <c r="M4" s="3">
+        <v>481</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/datos/motores.xlsx
+++ b/datos/motores.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Electrical_Engineering\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4BE601-45EC-44E9-B4C3-017CC4DDDD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543DF52B-923D-4E66-8417-995D8C045359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CF66B361-FEBB-41C8-94E9-5375418F99E3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{CF66B361-FEBB-41C8-94E9-5375418F99E3}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="MOTORES" sheetId="1" r:id="rId1"/>
+    <sheet name="MEDICIONES" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="95">
   <si>
     <t>TAG</t>
   </si>
@@ -42,24 +43,12 @@
     <t>HP</t>
   </si>
   <si>
-    <t>VOLTAJE</t>
-  </si>
-  <si>
     <t>FP</t>
   </si>
   <si>
     <t>EFICIENCIA</t>
   </si>
   <si>
-    <t>M-001</t>
-  </si>
-  <si>
-    <t>M-002</t>
-  </si>
-  <si>
-    <t>M-003</t>
-  </si>
-  <si>
     <t>CORRIENTE_PLACA_A</t>
   </si>
   <si>
@@ -87,23 +76,257 @@
     <t>ESTADO</t>
   </si>
   <si>
-    <t>Bomba de agua</t>
-  </si>
-  <si>
     <t>Operando</t>
   </si>
   <si>
-    <t>Ventilador</t>
-  </si>
-  <si>
-    <t>Bomba condensado</t>
+    <t>AREA</t>
+  </si>
+  <si>
+    <t>FABRICANTE</t>
+  </si>
+  <si>
+    <t>MODELO</t>
+  </si>
+  <si>
+    <t>TIPO_EQUIPO</t>
+  </si>
+  <si>
+    <t>KW_PLACA</t>
+  </si>
+  <si>
+    <t>VOLTAJE_V</t>
+  </si>
+  <si>
+    <t>FRECUENCIA_HZ</t>
+  </si>
+  <si>
+    <t>CLASE_EFICIENCIA</t>
+  </si>
+  <si>
+    <t>RPM_MOTOR</t>
+  </si>
+  <si>
+    <t>RPM_SALIDA</t>
+  </si>
+  <si>
+    <t>RELACION_REDUCCION</t>
+  </si>
+  <si>
+    <t>PAR_SALIDA_NM</t>
+  </si>
+  <si>
+    <t>SERVICIO</t>
+  </si>
+  <si>
+    <t>FACTOR_SERVICIO</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>CLASE_AISLAMIENTO</t>
+  </si>
+  <si>
+    <t>INVERTER_DUTY</t>
+  </si>
+  <si>
+    <t>TEMPERATURA_MIN_C</t>
+  </si>
+  <si>
+    <t>TEMPERATURA_MAX_C</t>
+  </si>
+  <si>
+    <t>LUBRICANTE</t>
+  </si>
+  <si>
+    <t>VOLUMEN_ACEITE_L</t>
+  </si>
+  <si>
+    <t>PESO_KG</t>
+  </si>
+  <si>
+    <t>FRENO</t>
+  </si>
+  <si>
+    <t>VOLTAJE_FRENO_V</t>
+  </si>
+  <si>
+    <t>PAR_FRENO_NM</t>
+  </si>
+  <si>
+    <t>OBSERVACIONES</t>
+  </si>
+  <si>
+    <t>MR-001</t>
+  </si>
+  <si>
+    <t>SEW-EURODRIVE</t>
+  </si>
+  <si>
+    <t>R97 DRN100L4/BES</t>
+  </si>
+  <si>
+    <t>Motorreductor</t>
+  </si>
+  <si>
+    <t>IE3</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>IP55</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>CLP 220 mineral</t>
+  </si>
+  <si>
+    <t>Pendiente inspección</t>
+  </si>
+  <si>
+    <t>Datos obtenidos de placa</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 1</t>
+  </si>
+  <si>
+    <t>SECADO MECANICO</t>
+  </si>
+  <si>
+    <t>MR-002</t>
+  </si>
+  <si>
+    <t>MR-003</t>
+  </si>
+  <si>
+    <t>MR-004</t>
+  </si>
+  <si>
+    <t>MR-005</t>
+  </si>
+  <si>
+    <t>MR-006</t>
+  </si>
+  <si>
+    <t>MR-007</t>
+  </si>
+  <si>
+    <t>MR-008</t>
+  </si>
+  <si>
+    <t>MR-009</t>
+  </si>
+  <si>
+    <t>MR-010</t>
+  </si>
+  <si>
+    <t>MR-011</t>
+  </si>
+  <si>
+    <t>MR-012</t>
+  </si>
+  <si>
+    <t>MR-013</t>
+  </si>
+  <si>
+    <t>MR-014</t>
+  </si>
+  <si>
+    <t>MR-015</t>
+  </si>
+  <si>
+    <t>MR-016</t>
+  </si>
+  <si>
+    <t>MR-017</t>
+  </si>
+  <si>
+    <t>MR-018</t>
+  </si>
+  <si>
+    <t>MR-019</t>
+  </si>
+  <si>
+    <t>MR-020</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 2</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 3</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 4</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 5</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 6</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 7</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 8</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 9</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 10</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 11</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 12</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 13</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 14</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 15</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 16</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 17</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 18</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 19</t>
+  </si>
+  <si>
+    <t>Motorreductor SEW - CILINDRO SECADORA 20</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>TEMPERATURA_C</t>
+  </si>
+  <si>
+    <t>AISLAMIENTO_MOHM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,6 +346,20 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -145,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -156,6 +393,32 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -471,200 +734,2389 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9F3007C-4CCE-4FA5-A545-AD73C08BCFA6}">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:AG21"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.08984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.08984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.1796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.26953125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="18.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="19.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="1" width="7.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.08984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.26953125" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.6328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.26953125" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.90625" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.90625" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.36328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18" style="4" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="23.6328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="24.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="21.7265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.36328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="23.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="AG1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="3">
-        <v>125</v>
-      </c>
-      <c r="D2" s="3">
-        <v>480</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0.88</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.94</v>
-      </c>
-      <c r="G2" s="3">
-        <v>140</v>
-      </c>
-      <c r="H2" s="3">
-        <v>118</v>
-      </c>
-      <c r="I2" s="3">
-        <v>120</v>
-      </c>
-      <c r="J2" s="3">
-        <v>123</v>
-      </c>
-      <c r="K2" s="3">
-        <v>478</v>
-      </c>
-      <c r="L2" s="3">
-        <v>481</v>
-      </c>
-      <c r="M2" s="3">
-        <v>479</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H2" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I2" s="8">
+        <v>480</v>
+      </c>
+      <c r="J2" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K2" s="8">
+        <v>60</v>
+      </c>
+      <c r="L2" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M2" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P2" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R2" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T2" s="8">
+        <v>1</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X2" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y2" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z2" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA2" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB2" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD2" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE2" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF2" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG2" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="3">
+        <v>73</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H3" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I3" s="8">
+        <v>480</v>
+      </c>
+      <c r="J3" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K3" s="8">
+        <v>60</v>
+      </c>
+      <c r="L3" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M3" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P3" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R3" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T3" s="8">
+        <v>1</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X3" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y3" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA3" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB3" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD3" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE3" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF3" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG3" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H4" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I4" s="8">
+        <v>480</v>
+      </c>
+      <c r="J4" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K4" s="8">
+        <v>60</v>
+      </c>
+      <c r="L4" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O4" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P4" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R4" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S4" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T4" s="8">
+        <v>1</v>
+      </c>
+      <c r="U4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V4" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X4" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y4" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA4" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB4" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD4" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE4" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF4" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG4" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="3">
-        <v>480</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.93</v>
-      </c>
-      <c r="G3" s="3">
+      <c r="C5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H5" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I5" s="8">
+        <v>480</v>
+      </c>
+      <c r="J5" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K5" s="8">
+        <v>60</v>
+      </c>
+      <c r="L5" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O5" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P5" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R5" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T5" s="8">
+        <v>1</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X5" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y5" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA5" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB5" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD5" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE5" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG5" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H6" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I6" s="8">
+        <v>480</v>
+      </c>
+      <c r="J6" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K6" s="8">
+        <v>60</v>
+      </c>
+      <c r="L6" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O6" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P6" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R6" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T6" s="8">
+        <v>1</v>
+      </c>
+      <c r="U6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X6" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y6" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE6" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF6" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG6" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H7" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I7" s="8">
+        <v>480</v>
+      </c>
+      <c r="J7" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K7" s="8">
+        <v>60</v>
+      </c>
+      <c r="L7" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O7" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P7" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R7" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S7" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T7" s="8">
+        <v>1</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X7" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y7" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA7" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB7" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD7" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE7" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG7" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H8" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I8" s="8">
+        <v>480</v>
+      </c>
+      <c r="J8" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K8" s="8">
+        <v>60</v>
+      </c>
+      <c r="L8" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M8" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O8" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P8" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R8" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T8" s="8">
+        <v>1</v>
+      </c>
+      <c r="U8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W8" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X8" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y8" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA8" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB8" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC8" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD8" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE8" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG8" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H9" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I9" s="8">
+        <v>480</v>
+      </c>
+      <c r="J9" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K9" s="8">
+        <v>60</v>
+      </c>
+      <c r="L9" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O9" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P9" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R9" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T9" s="8">
+        <v>1</v>
+      </c>
+      <c r="U9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X9" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y9" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA9" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB9" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD9" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE9" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG9" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H10" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I10" s="8">
+        <v>480</v>
+      </c>
+      <c r="J10" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K10" s="8">
+        <v>60</v>
+      </c>
+      <c r="L10" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M10" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O10" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P10" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R10" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S10" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T10" s="8">
+        <v>1</v>
+      </c>
+      <c r="U10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V10" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X10" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y10" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA10" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB10" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD10" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE10" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF10" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG10" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H11" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I11" s="8">
+        <v>480</v>
+      </c>
+      <c r="J11" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K11" s="8">
+        <v>60</v>
+      </c>
+      <c r="L11" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O11" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P11" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R11" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T11" s="8">
+        <v>1</v>
+      </c>
+      <c r="U11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V11" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W11" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X11" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y11" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA11" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB11" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC11" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD11" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE11" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG11" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H3" s="3">
-        <v>74</v>
-      </c>
-      <c r="I3" s="3">
-        <v>76</v>
-      </c>
-      <c r="J3" s="3">
-        <v>79</v>
-      </c>
-      <c r="K3" s="3">
-        <v>477</v>
-      </c>
-      <c r="L3" s="3">
-        <v>480</v>
-      </c>
-      <c r="M3" s="3">
-        <v>482</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="3">
-        <v>30</v>
-      </c>
-      <c r="D4" s="3">
-        <v>480</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0.87</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.91</v>
-      </c>
-      <c r="G4" s="3">
-        <v>35</v>
-      </c>
-      <c r="H4" s="3">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3">
-        <v>32</v>
-      </c>
-      <c r="J4" s="3">
-        <v>33</v>
-      </c>
-      <c r="K4" s="3">
-        <v>479</v>
-      </c>
-      <c r="L4" s="3">
-        <v>478</v>
-      </c>
-      <c r="M4" s="3">
-        <v>481</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>18</v>
+      <c r="C12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H12" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I12" s="8">
+        <v>480</v>
+      </c>
+      <c r="J12" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K12" s="8">
+        <v>60</v>
+      </c>
+      <c r="L12" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M12" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O12" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P12" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R12" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S12" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T12" s="8">
+        <v>1</v>
+      </c>
+      <c r="U12" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V12" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X12" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y12" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA12" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB12" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD12" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE12" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF12" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG12" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H13" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I13" s="8">
+        <v>480</v>
+      </c>
+      <c r="J13" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K13" s="8">
+        <v>60</v>
+      </c>
+      <c r="L13" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O13" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P13" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R13" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S13" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T13" s="8">
+        <v>1</v>
+      </c>
+      <c r="U13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X13" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y13" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z13" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD13" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE13" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF13" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG13" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H14" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I14" s="8">
+        <v>480</v>
+      </c>
+      <c r="J14" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K14" s="8">
+        <v>60</v>
+      </c>
+      <c r="L14" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M14" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O14" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P14" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R14" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S14" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T14" s="8">
+        <v>1</v>
+      </c>
+      <c r="U14" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V14" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X14" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y14" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z14" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA14" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB14" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD14" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE14" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF14" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG14" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H15" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I15" s="8">
+        <v>480</v>
+      </c>
+      <c r="J15" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K15" s="8">
+        <v>60</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O15" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P15" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R15" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S15" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T15" s="8">
+        <v>1</v>
+      </c>
+      <c r="U15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V15" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X15" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y15" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA15" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB15" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD15" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE15" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF15" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG15" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H16" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I16" s="8">
+        <v>480</v>
+      </c>
+      <c r="J16" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K16" s="8">
+        <v>60</v>
+      </c>
+      <c r="L16" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M16" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O16" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P16" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R16" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T16" s="8">
+        <v>1</v>
+      </c>
+      <c r="U16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V16" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X16" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y16" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA16" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB16" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD16" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE16" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF16" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG16" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H17" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I17" s="8">
+        <v>480</v>
+      </c>
+      <c r="J17" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K17" s="8">
+        <v>60</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O17" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P17" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R17" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S17" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T17" s="8">
+        <v>1</v>
+      </c>
+      <c r="U17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V17" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X17" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y17" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA17" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB17" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD17" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE17" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF17" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG17" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H18" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I18" s="8">
+        <v>480</v>
+      </c>
+      <c r="J18" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K18" s="8">
+        <v>60</v>
+      </c>
+      <c r="L18" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M18" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O18" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P18" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R18" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T18" s="8">
+        <v>1</v>
+      </c>
+      <c r="U18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V18" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W18" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X18" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y18" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z18" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA18" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB18" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC18" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD18" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE18" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF18" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG18" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H19" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I19" s="8">
+        <v>480</v>
+      </c>
+      <c r="J19" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K19" s="8">
+        <v>60</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O19" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P19" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R19" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S19" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T19" s="8">
+        <v>1</v>
+      </c>
+      <c r="U19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V19" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W19" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X19" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y19" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z19" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA19" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB19" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC19" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD19" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE19" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF19" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG19" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H20" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I20" s="8">
+        <v>480</v>
+      </c>
+      <c r="J20" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K20" s="8">
+        <v>60</v>
+      </c>
+      <c r="L20" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M20" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O20" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P20" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R20" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S20" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T20" s="8">
+        <v>1</v>
+      </c>
+      <c r="U20" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V20" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W20" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X20" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y20" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z20" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA20" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB20" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC20" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD20" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE20" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF20" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG20" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="H21" s="8">
+        <v>4.96</v>
+      </c>
+      <c r="I21" s="8">
+        <v>480</v>
+      </c>
+      <c r="J21" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="K21" s="8">
+        <v>60</v>
+      </c>
+      <c r="L21" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O21" s="8">
+        <v>1758</v>
+      </c>
+      <c r="P21" s="8">
+        <v>27</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>65.209999999999994</v>
+      </c>
+      <c r="R21" s="8">
+        <v>1310</v>
+      </c>
+      <c r="S21" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T21" s="8">
+        <v>1</v>
+      </c>
+      <c r="U21" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V21" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W21" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X21" s="8">
+        <v>-20</v>
+      </c>
+      <c r="Y21" s="8">
+        <v>40</v>
+      </c>
+      <c r="Z21" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA21" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AB21" s="8">
+        <v>143.37899999999999</v>
+      </c>
+      <c r="AC21" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD21" s="8">
+        <v>480</v>
+      </c>
+      <c r="AE21" s="8">
+        <v>55</v>
+      </c>
+      <c r="AF21" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG21" s="8" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B61A613-5127-46A3-983F-C72B10EE762D}">
+  <dimension ref="A1:L23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="15.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="9">
+        <v>5.8</v>
+      </c>
+      <c r="D2" s="9">
+        <v>5.9</v>
+      </c>
+      <c r="E2" s="9">
+        <v>6</v>
+      </c>
+      <c r="F2" s="9">
+        <v>478</v>
+      </c>
+      <c r="G2" s="9">
+        <v>480</v>
+      </c>
+      <c r="H2" s="9">
+        <v>479</v>
+      </c>
+      <c r="I2" s="9">
+        <v>52</v>
+      </c>
+      <c r="J2" s="9">
+        <v>850</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="9">
+        <v>6.1</v>
+      </c>
+      <c r="D3" s="9">
+        <v>6</v>
+      </c>
+      <c r="E3" s="9">
+        <v>6.2</v>
+      </c>
+      <c r="F3" s="9">
+        <v>479</v>
+      </c>
+      <c r="G3" s="9">
+        <v>481</v>
+      </c>
+      <c r="H3" s="9">
+        <v>480</v>
+      </c>
+      <c r="I3" s="9">
+        <v>55</v>
+      </c>
+      <c r="J3" s="9">
+        <v>720</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="9">
+        <v>5.9</v>
+      </c>
+      <c r="D4" s="9">
+        <v>6.1</v>
+      </c>
+      <c r="E4" s="9">
+        <v>6</v>
+      </c>
+      <c r="F4" s="9">
+        <v>477</v>
+      </c>
+      <c r="G4" s="9">
+        <v>480</v>
+      </c>
+      <c r="H4" s="9">
+        <v>479</v>
+      </c>
+      <c r="I4" s="9">
+        <v>54</v>
+      </c>
+      <c r="J4" s="9">
+        <v>810</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="6"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="5"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="5"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="5"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="5"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="5"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="5"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="5"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="5"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" s="5"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" s="5"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" s="5"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="5"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="5"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="5"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="5"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="5"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>